--- a/data/trans_orig/P19E-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19E-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que se cepilla los dientes al día en 2016</t>
+          <t>Población según el número de veces que se cepilla los dientes al día en 2016 (tasa de respuesta: 97,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>166171</t>
+          <t>167032</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>214038</t>
+          <t>212467</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>207544</t>
+          <t>208249</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>259262</t>
+          <t>256375</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>387317</t>
+          <t>387509</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>453960</t>
+          <t>458225</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,89%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>186937</t>
+          <t>191909</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>236525</t>
+          <t>237191</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>207603</t>
+          <t>206251</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>257143</t>
+          <t>255291</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>410758</t>
+          <t>409778</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>477873</t>
+          <t>477145</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>133509</t>
+          <t>134164</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>176831</t>
+          <t>177447</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>131549</t>
+          <t>132535</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>174259</t>
+          <t>172862</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>275278</t>
+          <t>276315</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>337396</t>
+          <t>335949</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,58%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15014</t>
+          <t>15131</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34489</t>
+          <t>34465</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7956</t>
+          <t>8690</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24920</t>
+          <t>24094</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27443</t>
+          <t>27309</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52347</t>
+          <t>51123</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57279</t>
+          <t>56673</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89984</t>
+          <t>90839</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20822</t>
+          <t>21662</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44701</t>
+          <t>44753</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>85490</t>
+          <t>85688</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>124035</t>
+          <t>124923</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>304914</t>
+          <t>304876</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>365537</t>
+          <t>367566</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>388867</t>
+          <t>389031</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>453812</t>
+          <t>454537</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>711413</t>
+          <t>712311</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>801203</t>
+          <t>799606</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>278623</t>
+          <t>277144</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>339634</t>
+          <t>336150</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>330239</t>
+          <t>327469</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>391002</t>
+          <t>391167</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>622300</t>
+          <t>627527</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>710567</t>
+          <t>714200</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,09%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>234617</t>
+          <t>239592</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>291897</t>
+          <t>295559</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>169860</t>
+          <t>168748</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>218817</t>
+          <t>219424</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>420768</t>
+          <t>414554</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>499267</t>
+          <t>492423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14557</t>
+          <t>15711</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35378</t>
+          <t>36386</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24263</t>
+          <t>24215</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26335</t>
+          <t>26581</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52461</t>
+          <t>53180</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58006</t>
+          <t>59486</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93228</t>
+          <t>93128</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29472</t>
+          <t>30122</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>55139</t>
+          <t>56864</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94821</t>
+          <t>96122</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>138763</t>
+          <t>141075</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>206117</t>
+          <t>205202</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>258581</t>
+          <t>258113</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>287040</t>
+          <t>288453</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>342685</t>
+          <t>343313</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>508995</t>
+          <t>509928</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>583579</t>
+          <t>587453</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,92%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>167750</t>
+          <t>168389</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>215513</t>
+          <t>219137</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>202244</t>
+          <t>200531</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>251568</t>
+          <t>251419</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>383158</t>
+          <t>380818</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>451604</t>
+          <t>451342</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>187853</t>
+          <t>187838</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>237962</t>
+          <t>237970</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>136854</t>
+          <t>136326</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182298</t>
+          <t>183088</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>341021</t>
+          <t>338470</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>408150</t>
+          <t>408662</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20124</t>
+          <t>19793</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43249</t>
+          <t>42806</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14688</t>
+          <t>14766</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36204</t>
+          <t>36772</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39830</t>
+          <t>38644</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71248</t>
+          <t>69065</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42286</t>
+          <t>42944</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>71696</t>
+          <t>73243</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17402</t>
+          <t>16452</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>39919</t>
+          <t>38029</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>64737</t>
+          <t>65088</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>100996</t>
+          <t>101201</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>374365</t>
+          <t>375928</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>433260</t>
+          <t>433820</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>496424</t>
+          <t>497197</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>564302</t>
+          <t>567729</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>887575</t>
+          <t>893113</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>979945</t>
+          <t>981013</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,74%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>250123</t>
+          <t>251445</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>306267</t>
+          <t>307788</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>283757</t>
+          <t>281336</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>346737</t>
+          <t>342745</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>552809</t>
+          <t>553912</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>634919</t>
+          <t>634999</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>150964</t>
+          <t>150120</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>196473</t>
+          <t>196895</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>112089</t>
+          <t>114935</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>162651</t>
+          <t>161358</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,39 +3053,39 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
+          <t>15,88%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>309521</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>276954</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>342430</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
           <t>16,01%</t>
         </is>
       </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>309521</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>276943</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>340449</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>16,01%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
           <t>14,32%</t>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13912</t>
+          <t>13949</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>31246</t>
+          <t>32851</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4314</t>
+          <t>4565</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19173</t>
+          <t>19494</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22333</t>
+          <t>22400</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>45509</t>
+          <t>44742</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>27505</t>
+          <t>28343</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>52231</t>
+          <t>53470</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15676</t>
+          <t>15784</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>37522</t>
+          <t>37458</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>49070</t>
+          <t>50530</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>81677</t>
+          <t>83269</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1103420</t>
+          <t>1100283</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1220728</t>
+          <t>1215794</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1442619</t>
+          <t>1440558</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1557325</t>
+          <t>1561363</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2579294</t>
+          <t>2571155</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2736284</t>
+          <t>2738379</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,55%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>933260</t>
+          <t>940335</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1041499</t>
+          <t>1044347</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1075837</t>
+          <t>1074833</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1188330</t>
+          <t>1187888</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2044205</t>
+          <t>2044869</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2197429</t>
+          <t>2189857</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,42%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>751812</t>
+          <t>756770</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>851831</t>
+          <t>857481</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>595021</t>
+          <t>598814</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>685391</t>
+          <t>688044</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1380698</t>
+          <t>1375725</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1510638</t>
+          <t>1514181</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,42%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>79374</t>
+          <t>80014</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>119243</t>
+          <t>120620</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>47192</t>
+          <t>46451</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>80113</t>
+          <t>81015</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>137078</t>
+          <t>137526</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>188277</t>
+          <t>190446</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>215499</t>
+          <t>211718</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>275557</t>
+          <t>274402</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>102234</t>
+          <t>101276</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>147562</t>
+          <t>151579</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>331996</t>
+          <t>332526</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>405798</t>
+          <t>407114</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -4178,7 +4178,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que se cepilla los dientes al día en 2023</t>
+          <t>Población según el número de veces que se cepilla los dientes al día en 2023 (tasa de respuesta: 99,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>112338</t>
+          <t>111152</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>167037</t>
+          <t>169383</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>172105</t>
+          <t>173115</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>213073</t>
+          <t>211930</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>297115</t>
+          <t>295385</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>362529</t>
+          <t>366362</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>250815</t>
+          <t>253446</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>305392</t>
+          <t>305590</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>323495</t>
+          <t>323571</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>364172</t>
+          <t>365079</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>590714</t>
+          <t>589965</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>655307</t>
+          <t>661209</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,89%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>149823</t>
+          <t>151367</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>196235</t>
+          <t>194818</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>91623</t>
+          <t>91596</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>121066</t>
+          <t>118848</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>250881</t>
+          <t>252181</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>302056</t>
+          <t>304697</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>6820</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19808</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7784</t>
+          <t>8227</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18988</t>
+          <t>19403</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18104</t>
+          <t>17364</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33765</t>
+          <t>33252</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20260</t>
+          <t>19594</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38816</t>
+          <t>38457</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12946</t>
+          <t>13286</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24438</t>
+          <t>25262</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>36538</t>
+          <t>36368</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>58629</t>
+          <t>58252</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>236188</t>
+          <t>232665</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>791888</t>
+          <t>830941</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>278225</t>
+          <t>278723</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>329323</t>
+          <t>333659</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>550615</t>
+          <t>551365</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1191929</t>
+          <t>1252915</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>58,45%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281394</t>
+          <t>256016</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>676868</t>
+          <t>680815</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>454674</t>
+          <t>454414</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>511251</t>
+          <t>506485</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>690386</t>
+          <t>649270</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1158783</t>
+          <t>1156620</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>53,96%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>96652</t>
+          <t>86324</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>235270</t>
+          <t>238461</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>113034</t>
+          <t>113637</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>147326</t>
+          <t>149583</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>194931</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>359757</t>
+          <t>362821</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7052</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24937</t>
+          <t>24672</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>8050</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18957</t>
+          <t>19355</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17645</t>
+          <t>17541</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38342</t>
+          <t>38916</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13743</t>
+          <t>13138</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41717</t>
+          <t>42229</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18119</t>
+          <t>18076</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33871</t>
+          <t>33475</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35392</t>
+          <t>35084</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>70076</t>
+          <t>69407</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>111214</t>
+          <t>109208</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>161841</t>
+          <t>159257</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>114411</t>
+          <t>122919</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>315001</t>
+          <t>312278</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>240662</t>
+          <t>236767</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>460596</t>
+          <t>446767</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,33%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>339769</t>
+          <t>341807</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>402382</t>
+          <t>404914</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>469079</t>
+          <t>471270</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>742274</t>
+          <t>742874</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>835228</t>
+          <t>838947</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1175336</t>
+          <t>1188744</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>72,71%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>138716</t>
+          <t>138911</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>187127</t>
+          <t>188862</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>52636</t>
+          <t>51423</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>133759</t>
+          <t>134026</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>172204</t>
+          <t>167191</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>312306</t>
+          <t>311006</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15788</t>
+          <t>15887</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>702</t>
+          <t>862</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5748</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19246</t>
+          <t>20421</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19403</t>
+          <t>18205</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39739</t>
+          <t>40333</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8728</t>
+          <t>8842</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28174</t>
+          <t>29080</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>29142</t>
+          <t>29197</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>63144</t>
+          <t>62075</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>222087</t>
+          <t>219591</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>280602</t>
+          <t>275971</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>293878</t>
+          <t>300249</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>407034</t>
+          <t>409332</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>539809</t>
+          <t>548157</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>663231</t>
+          <t>667956</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -6532,12 +6532,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>441553</t>
+          <t>443205</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>509515</t>
+          <t>510361</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6547,12 +6547,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>527581</t>
+          <t>528313</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>693293</t>
+          <t>679719</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6582,12 +6582,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>994051</t>
+          <t>993072</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1158690</t>
+          <t>1157563</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6617,12 +6617,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,63%</t>
         </is>
       </c>
     </row>
@@ -6645,12 +6645,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>141994</t>
+          <t>141170</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>188181</t>
+          <t>188018</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6660,12 +6660,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>93947</t>
+          <t>93220</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>135701</t>
+          <t>137115</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>244406</t>
+          <t>247530</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>313371</t>
+          <t>316973</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19858</t>
+          <t>19968</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5758</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15643</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6808,12 +6808,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15601</t>
+          <t>15255</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32522</t>
+          <t>31782</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6843,12 +6843,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -6871,12 +6871,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13060</t>
+          <t>13020</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>33064</t>
+          <t>31696</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6906,12 +6906,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10877</t>
+          <t>11124</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25308</t>
+          <t>25345</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>27967</t>
+          <t>27728</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>51665</t>
+          <t>51147</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6956,12 +6956,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>751747</t>
+          <t>751121</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1482760</t>
+          <t>1485227</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>899231</t>
+          <t>887641</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1197213</t>
+          <t>1188041</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1818475</t>
+          <t>1826196</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2687501</t>
+          <t>2633255</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -7209,17 +7209,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1654233</t>
+          <t>1654234</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1322834</t>
+          <t>1275541</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1803736</t>
+          <t>1798859</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1848675</t>
+          <t>1855371</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2301239</t>
+          <t>2298583</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3268681</t>
+          <t>3276998</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3926664</t>
+          <t>3911781</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7299,12 +7299,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,2%</t>
         </is>
       </c>
     </row>
@@ -7327,12 +7327,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>534860</t>
+          <t>522817</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>753854</t>
+          <t>755701</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7362,12 +7362,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>372497</t>
+          <t>362353</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>493686</t>
+          <t>493292</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>965977</t>
+          <t>987266</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1221945</t>
+          <t>1221534</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -7440,12 +7440,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>35124</t>
+          <t>33638</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>62001</t>
+          <t>62391</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7455,12 +7455,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>29186</t>
+          <t>29231</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>49698</t>
+          <t>49429</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7510,12 +7510,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>68324</t>
+          <t>70028</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>104484</t>
+          <t>103876</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -7553,12 +7553,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>80013</t>
+          <t>81219</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>127177</t>
+          <t>126818</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7568,12 +7568,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>61519</t>
+          <t>62016</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>93865</t>
+          <t>93088</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7603,47 +7603,47 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>183146</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>153818</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>211572</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
           <t>2,58%</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>183146</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>156317</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>212659</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19E-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19E-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>167032</t>
+          <t>166620</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>212467</t>
+          <t>214277</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>208249</t>
+          <t>205592</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>256375</t>
+          <t>257281</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>387509</t>
+          <t>388173</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>458225</t>
+          <t>457282</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,82%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>191909</t>
+          <t>189086</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>237191</t>
+          <t>237674</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>206251</t>
+          <t>207707</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>255291</t>
+          <t>255056</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>409778</t>
+          <t>408821</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>477145</t>
+          <t>479048</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,47%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>134164</t>
+          <t>136071</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>177447</t>
+          <t>175719</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>132535</t>
+          <t>131548</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>172862</t>
+          <t>175876</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>276315</t>
+          <t>277233</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>335949</t>
+          <t>339403</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15131</t>
+          <t>14744</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34465</t>
+          <t>35030</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8690</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24094</t>
+          <t>23993</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27309</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51123</t>
+          <t>51864</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>56673</t>
+          <t>58160</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90839</t>
+          <t>92037</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21662</t>
+          <t>21120</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44753</t>
+          <t>44557</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>85688</t>
+          <t>83631</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>124923</t>
+          <t>125269</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>304876</t>
+          <t>303543</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>367566</t>
+          <t>369456</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>389031</t>
+          <t>390052</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>454537</t>
+          <t>454850</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>712311</t>
+          <t>710968</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>799606</t>
+          <t>801083</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,36%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>277144</t>
+          <t>278717</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>336150</t>
+          <t>338018</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327469</t>
+          <t>328188</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>391167</t>
+          <t>389864</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>627527</t>
+          <t>625951</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>714200</t>
+          <t>708528</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,82%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>239592</t>
+          <t>236194</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>295559</t>
+          <t>294122</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>168748</t>
+          <t>169695</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>219424</t>
+          <t>219676</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>414554</t>
+          <t>419266</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>492423</t>
+          <t>499895</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15711</t>
+          <t>15194</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36386</t>
+          <t>35969</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>8209</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24215</t>
+          <t>23923</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26581</t>
+          <t>26379</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53180</t>
+          <t>53556</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59486</t>
+          <t>59379</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93128</t>
+          <t>95421</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>30122</t>
+          <t>29577</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56864</t>
+          <t>55174</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>96122</t>
+          <t>95811</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>141075</t>
+          <t>140703</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>205202</t>
+          <t>207400</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>258113</t>
+          <t>260293</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>288453</t>
+          <t>287165</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>343313</t>
+          <t>342033</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>509928</t>
+          <t>510761</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>587453</t>
+          <t>586732</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,87%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168389</t>
+          <t>165894</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>219137</t>
+          <t>216389</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>200531</t>
+          <t>200418</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>251419</t>
+          <t>253581</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>380818</t>
+          <t>381060</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>451342</t>
+          <t>451403</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>187838</t>
+          <t>187730</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>237970</t>
+          <t>239967</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>136326</t>
+          <t>137514</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>183088</t>
+          <t>184855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>338470</t>
+          <t>334234</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>408662</t>
+          <t>406222</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,6%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19793</t>
+          <t>19444</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42806</t>
+          <t>43174</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14766</t>
+          <t>15064</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36772</t>
+          <t>38502</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38644</t>
+          <t>40080</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>69065</t>
+          <t>73251</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42944</t>
+          <t>42468</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>73243</t>
+          <t>72693</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16452</t>
+          <t>16903</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38029</t>
+          <t>37783</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>65088</t>
+          <t>64678</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>101201</t>
+          <t>101669</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>375928</t>
+          <t>372415</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>433820</t>
+          <t>437391</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>497197</t>
+          <t>491343</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>567729</t>
+          <t>560392</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>893113</t>
+          <t>886412</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>981013</t>
+          <t>976625</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,51%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>251445</t>
+          <t>250710</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>307788</t>
+          <t>306125</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>281336</t>
+          <t>284821</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>342745</t>
+          <t>344726</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>553912</t>
+          <t>552129</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>634999</t>
+          <t>636783</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>150120</t>
+          <t>148113</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>196895</t>
+          <t>196133</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>114935</t>
+          <t>114689</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>161358</t>
+          <t>163340</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>276954</t>
+          <t>276639</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>342430</t>
+          <t>341878</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13949</t>
+          <t>14168</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32851</t>
+          <t>32388</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19494</t>
+          <t>19674</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22400</t>
+          <t>22623</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>44742</t>
+          <t>46107</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>28343</t>
+          <t>28297</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>53470</t>
+          <t>54902</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>15784</t>
+          <t>15895</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>37458</t>
+          <t>38236</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>50530</t>
+          <t>50436</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>83269</t>
+          <t>83643</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1100283</t>
+          <t>1110462</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1215794</t>
+          <t>1223826</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1440558</t>
+          <t>1446213</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1561363</t>
+          <t>1564130</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2571155</t>
+          <t>2572904</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2738379</t>
+          <t>2737292</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>40,53%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>940335</t>
+          <t>937875</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1044347</t>
+          <t>1038558</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1074833</t>
+          <t>1074389</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1187888</t>
+          <t>1185600</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2044869</t>
+          <t>2057948</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2189857</t>
+          <t>2211712</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,75%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>756770</t>
+          <t>754717</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>857481</t>
+          <t>855965</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>598814</t>
+          <t>594866</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>688044</t>
+          <t>684666</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1375725</t>
+          <t>1376762</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1514181</t>
+          <t>1517562</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>80014</t>
+          <t>81382</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>120620</t>
+          <t>118809</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>46451</t>
+          <t>48552</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>81015</t>
+          <t>80678</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>137526</t>
+          <t>134713</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>190446</t>
+          <t>189243</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>211718</t>
+          <t>212137</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>274402</t>
+          <t>272839</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>101276</t>
+          <t>100645</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>151579</t>
+          <t>146944</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>332526</t>
+          <t>329157</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>407114</t>
+          <t>402284</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -4368,32 +4368,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>136927</t>
+          <t>147002</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>111152</t>
+          <t>122630</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>169383</t>
+          <t>173410</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4403,32 +4403,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>191428</t>
+          <t>209674</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>173115</t>
+          <t>189712</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>211930</t>
+          <t>232212</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4438,32 +4438,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>328355</t>
+          <t>356677</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>295385</t>
+          <t>326370</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>366362</t>
+          <t>392606</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -4481,32 +4481,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>279535</t>
+          <t>307214</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>253446</t>
+          <t>280033</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>305590</t>
+          <t>332563</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>45,04%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4516,32 +4516,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>343664</t>
+          <t>375890</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>323571</t>
+          <t>354017</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>365079</t>
+          <t>397278</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4551,32 +4551,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>623199</t>
+          <t>683104</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>589965</t>
+          <t>641090</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>661209</t>
+          <t>716996</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,41%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,87%</t>
         </is>
       </c>
     </row>
@@ -4594,32 +4594,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>172500</t>
+          <t>186570</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>151367</t>
+          <t>163471</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>194818</t>
+          <t>211157</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4629,32 +4629,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>104651</t>
+          <t>110086</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>91596</t>
+          <t>94976</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>118848</t>
+          <t>125349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4664,32 +4664,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>277151</t>
+          <t>296655</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>252181</t>
+          <t>270540</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>304697</t>
+          <t>328591</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,31%</t>
         </is>
       </c>
     </row>
@@ -4707,67 +4707,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11808</t>
+          <t>12280</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>7494</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>19116</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>13671</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>9142</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>20280</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>1,88%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>12621</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>8227</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>19403</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4777,22 +4777,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>24430</t>
+          <t>25951</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17364</t>
+          <t>18861</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33252</t>
+          <t>35572</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -4820,32 +4820,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>28264</t>
+          <t>28971</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19594</t>
+          <t>21074</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>38457</t>
+          <t>40556</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4855,32 +4855,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17916</t>
+          <t>18193</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13286</t>
+          <t>13116</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25262</t>
+          <t>24771</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4890,32 +4890,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>46180</t>
+          <t>47163</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>36368</t>
+          <t>38069</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>58252</t>
+          <t>59332</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -4933,17 +4933,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>629035</t>
+          <t>682036</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>629035</t>
+          <t>682036</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>629035</t>
+          <t>682036</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4968,17 +4968,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>670280</t>
+          <t>727514</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>670280</t>
+          <t>727514</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>670280</t>
+          <t>727514</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5003,17 +5003,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1299315</t>
+          <t>1409550</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1299315</t>
+          <t>1409550</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1299315</t>
+          <t>1409550</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5050,32 +5050,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>440387</t>
+          <t>228669</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>232665</t>
+          <t>200146</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>830941</t>
+          <t>264311</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5085,32 +5085,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>303846</t>
+          <t>340745</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>278723</t>
+          <t>313335</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>333659</t>
+          <t>368414</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5120,32 +5120,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>744233</t>
+          <t>569414</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>551365</t>
+          <t>521086</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1252915</t>
+          <t>606271</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -5163,32 +5163,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>528459</t>
+          <t>582457</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>256016</t>
+          <t>545666</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680815</t>
+          <t>618973</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>52,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5198,27 +5198,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>481615</t>
+          <t>537518</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>454414</t>
+          <t>509452</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>506485</t>
+          <t>565710</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5233,32 +5233,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1010074</t>
+          <t>1119975</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>649270</t>
+          <t>1075580</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1156620</t>
+          <t>1172159</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>55,53%</t>
         </is>
       </c>
     </row>
@@ -5276,32 +5276,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>179353</t>
+          <t>188379</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>86324</t>
+          <t>160655</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>238461</t>
+          <t>215805</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5311,32 +5311,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>129394</t>
+          <t>144064</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>113637</t>
+          <t>124284</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>149583</t>
+          <t>162511</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5346,32 +5346,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>308748</t>
+          <t>332443</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>205665</t>
+          <t>299490</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>362821</t>
+          <t>368486</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,46%</t>
         </is>
       </c>
     </row>
@@ -5389,32 +5389,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15028</t>
+          <t>18404</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6675</t>
+          <t>11387</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24672</t>
+          <t>29647</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5424,32 +5424,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12480</t>
+          <t>14858</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>10034</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19355</t>
+          <t>22466</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5459,32 +5459,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>27508</t>
+          <t>33262</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17541</t>
+          <t>23952</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38916</t>
+          <t>46089</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -5502,32 +5502,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>28296</t>
+          <t>29597</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13138</t>
+          <t>20837</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42229</t>
+          <t>40971</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5537,32 +5537,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>24718</t>
+          <t>26254</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18076</t>
+          <t>19072</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33475</t>
+          <t>35111</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>53014</t>
+          <t>55851</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>35084</t>
+          <t>44612</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>69407</t>
+          <t>72664</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -5615,17 +5615,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1191524</t>
+          <t>1047506</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1191524</t>
+          <t>1047506</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1191524</t>
+          <t>1047506</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5650,17 +5650,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>952053</t>
+          <t>1063439</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>952053</t>
+          <t>1063439</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>952053</t>
+          <t>1063439</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5685,17 +5685,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2143577</t>
+          <t>2110945</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2143577</t>
+          <t>2110945</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2143577</t>
+          <t>2110945</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5732,32 +5732,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>133664</t>
+          <t>162219</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109208</t>
+          <t>136203</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>159257</t>
+          <t>192261</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5767,32 +5767,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>229674</t>
+          <t>225263</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>122919</t>
+          <t>202711</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>312278</t>
+          <t>250924</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5802,32 +5802,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>363338</t>
+          <t>387481</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>236767</t>
+          <t>353559</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>446767</t>
+          <t>424714</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -5845,32 +5845,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>370695</t>
+          <t>415369</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>341807</t>
+          <t>378980</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>404914</t>
+          <t>447085</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>52,67%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>582357</t>
+          <t>446251</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>471270</t>
+          <t>420034</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>742874</t>
+          <t>472387</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>953052</t>
+          <t>861620</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>838947</t>
+          <t>818776</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1188744</t>
+          <t>903483</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>56,08%</t>
         </is>
       </c>
     </row>
@@ -5958,32 +5958,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>162662</t>
+          <t>184653</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>138911</t>
+          <t>160310</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>188862</t>
+          <t>212936</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5993,32 +5993,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>98099</t>
+          <t>116598</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>51423</t>
+          <t>98924</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>134026</t>
+          <t>134135</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>260761</t>
+          <t>301252</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>167191</t>
+          <t>271262</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>311006</t>
+          <t>335269</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -6071,32 +6071,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8581</t>
+          <t>9051</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4280</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15887</t>
+          <t>16613</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6106,32 +6106,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>9734</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>11576</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20421</t>
+          <t>21076</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -6184,32 +6184,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>28239</t>
+          <t>30016</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18205</t>
+          <t>19802</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>42823</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6219,32 +6219,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>17915</t>
+          <t>18102</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8842</t>
+          <t>11577</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29080</t>
+          <t>26092</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6254,32 +6254,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>46154</t>
+          <t>48119</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>29197</t>
+          <t>35500</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>62075</t>
+          <t>63230</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -6297,17 +6297,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>703840</t>
+          <t>801308</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>703840</t>
+          <t>801308</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>703840</t>
+          <t>801308</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6332,17 +6332,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>931040</t>
+          <t>809732</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>931040</t>
+          <t>809732</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>931040</t>
+          <t>809732</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1634881</t>
+          <t>1611040</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1634881</t>
+          <t>1611040</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1634881</t>
+          <t>1611040</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6414,32 +6414,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>248883</t>
+          <t>279382</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>219591</t>
+          <t>249638</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>275971</t>
+          <t>309863</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6449,32 +6449,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>369530</t>
+          <t>403165</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>300249</t>
+          <t>373146</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>409332</t>
+          <t>431660</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6484,32 +6484,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>618414</t>
+          <t>682547</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>548157</t>
+          <t>641397</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>667956</t>
+          <t>724917</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>34,58%</t>
         </is>
       </c>
     </row>
@@ -6527,32 +6527,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>475544</t>
+          <t>502795</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>443205</t>
+          <t>472462</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>510361</t>
+          <t>536108</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6562,32 +6562,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>573385</t>
+          <t>551834</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>528313</t>
+          <t>523270</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>679719</t>
+          <t>582250</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6597,32 +6597,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1048929</t>
+          <t>1054629</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>993072</t>
+          <t>1013230</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1157563</t>
+          <t>1104657</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>52,7%</t>
         </is>
       </c>
     </row>
@@ -6640,32 +6640,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>164196</t>
+          <t>167580</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>141170</t>
+          <t>143170</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>188018</t>
+          <t>191941</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6675,32 +6675,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>116884</t>
+          <t>127507</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>93220</t>
+          <t>109199</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>137115</t>
+          <t>143572</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6710,32 +6710,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>281080</t>
+          <t>295088</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>247530</t>
+          <t>266897</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>316973</t>
+          <t>324615</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -6753,32 +6753,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>11926</t>
+          <t>12170</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>6609</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19968</t>
+          <t>19960</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6788,32 +6788,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>10349</t>
+          <t>11676</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6169</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>18121</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6823,32 +6823,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>22275</t>
+          <t>23846</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15255</t>
+          <t>16520</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31782</t>
+          <t>32532</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -6866,32 +6866,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>20506</t>
+          <t>22349</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13020</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>31696</t>
+          <t>33748</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6901,32 +6901,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>17292</t>
+          <t>17779</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11124</t>
+          <t>11722</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25345</t>
+          <t>26559</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6936,27 +6936,27 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>37798</t>
+          <t>40128</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>27728</t>
+          <t>29755</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>51147</t>
+          <t>53451</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>921055</t>
+          <t>984276</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>921055</t>
+          <t>984276</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>921055</t>
+          <t>984276</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7014,17 +7014,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1087440</t>
+          <t>1111962</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1087440</t>
+          <t>1111962</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1087440</t>
+          <t>1111962</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7049,17 +7049,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>2008496</t>
+          <t>2096238</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>2008496</t>
+          <t>2096238</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2008496</t>
+          <t>2096238</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7096,32 +7096,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>959861</t>
+          <t>817272</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>751121</t>
+          <t>759590</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1485227</t>
+          <t>877719</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7131,32 +7131,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1094478</t>
+          <t>1178847</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>887641</t>
+          <t>1132618</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1188041</t>
+          <t>1231677</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7166,32 +7166,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2054339</t>
+          <t>1996119</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1826196</t>
+          <t>1921674</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2633255</t>
+          <t>2074178</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>28,7%</t>
         </is>
       </c>
     </row>
@@ -7209,32 +7209,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1654234</t>
+          <t>1807833</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1275541</t>
+          <t>1744460</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1798859</t>
+          <t>1876095</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7244,32 +7244,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1981020</t>
+          <t>1911494</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1855371</t>
+          <t>1858606</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2298583</t>
+          <t>1964311</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7279,32 +7279,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3635254</t>
+          <t>3719327</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3276998</t>
+          <t>3627151</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3911781</t>
+          <t>3799616</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,46%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>52,57%</t>
         </is>
       </c>
     </row>
@@ -7322,32 +7322,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>678711</t>
+          <t>727182</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>522817</t>
+          <t>680580</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>755701</t>
+          <t>783093</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7357,32 +7357,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>449028</t>
+          <t>498256</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>362353</t>
+          <t>464805</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>493292</t>
+          <t>537252</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7392,32 +7392,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1127740</t>
+          <t>1225438</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>987266</t>
+          <t>1166955</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1221534</t>
+          <t>1289285</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -7435,32 +7435,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>47343</t>
+          <t>51905</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>33638</t>
+          <t>39665</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>62391</t>
+          <t>67206</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7470,32 +7470,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>38446</t>
+          <t>43723</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>29231</t>
+          <t>33702</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>49429</t>
+          <t>54210</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7505,32 +7505,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>85789</t>
+          <t>95628</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>70028</t>
+          <t>78318</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>103876</t>
+          <t>114251</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -7548,32 +7548,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>105304</t>
+          <t>110932</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>81219</t>
+          <t>92706</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>126818</t>
+          <t>132598</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7583,32 +7583,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>77842</t>
+          <t>80328</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>62016</t>
+          <t>67222</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>93088</t>
+          <t>94697</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7618,32 +7618,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>183146</t>
+          <t>191261</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>153818</t>
+          <t>167070</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>211572</t>
+          <t>217230</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -7661,17 +7661,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>3445454</t>
+          <t>3515125</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3445454</t>
+          <t>3515125</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>3445454</t>
+          <t>3515125</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7696,17 +7696,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3640813</t>
+          <t>3712648</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>3640813</t>
+          <t>3712648</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3640813</t>
+          <t>3712648</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7731,17 +7731,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>7086268</t>
+          <t>7227773</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>7086268</t>
+          <t>7227773</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7086268</t>
+          <t>7227773</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
